--- a/output/pdf_financials_xlsx/FTUR.xlsx
+++ b/output/pdf_financials_xlsx/FTUR.xlsx
@@ -1002,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.009781</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.023873</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1014,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004469</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004266</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.001362</v>
       </c>
     </row>
     <row r="13">
@@ -1900,10 +1900,10 @@
         <v>-0.155554</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.159712</v>
+        <v>-0.169493</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.388895</v>
+        <v>-0.412768</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.154449</v>
@@ -1912,10 +1912,10 @@
         <v>-0.365238</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.555527</v>
+        <v>-0.551058</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.842981</v>
+        <v>-0.838715</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.352775</v>
@@ -1927,7 +1927,7 @@
         <v>-0.278039</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.585463</v>
+        <v>-2.586825</v>
       </c>
     </row>
     <row r="28">
@@ -2008,10 +2008,10 @@
         <v>-0.155554</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.159712</v>
+        <v>-0.169493</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.388895</v>
+        <v>-0.412768</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.154449</v>
@@ -2020,10 +2020,10 @@
         <v>-0.365238</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.555527</v>
+        <v>-0.551058</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.842981</v>
+        <v>-0.838715</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.352775</v>
@@ -2035,7 +2035,7 @@
         <v>-0.278039</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.585463</v>
+        <v>-2.586825</v>
       </c>
     </row>
     <row r="30">
@@ -2291,28 +2291,28 @@
         <v>0.000397</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.000422</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.277639</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.053867</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.13335</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.488254</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.522651</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.056106</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.054501</v>
       </c>
     </row>
     <row r="35">
@@ -2395,28 +2395,28 @@
         <v>0.000397</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.000422</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.6</v>
+        <v>0.8776389999999999</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.5</v>
+        <v>0.553867</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.126388</v>
+        <v>0.259738</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.114722</v>
+        <v>0.602976</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.068055</v>
+        <v>0.590706</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.052499</v>
+        <v>0.108605</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.014388</v>
+        <v>0.06888900000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3019,28 +3019,28 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.002665</v>
+        <v>0.002243</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.279634</v>
+        <v>0.001995</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.145593</v>
+        <v>0.091726</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.13867</v>
+        <v>0.00532</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.607342</v>
+        <v>0.119088</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.5243139999999999</v>
+        <v>0.001663</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.057744</v>
+        <v>0.001638</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.054501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -21329,7 +21329,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -21970,7 +21970,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">

--- a/output/pdf_financials_xlsx/FTUR.xlsx
+++ b/output/pdf_financials_xlsx/FTUR.xlsx
@@ -1284,7 +1284,7 @@
         <v>-0</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.13131</v>
+        <v>-0.13131</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>-0</v>
@@ -6452,13 +6452,13 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.003779</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.005287</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0</v>
+        <v>0.004022</v>
       </c>
       <c r="P110" s="3" t="n">
         <v>0</v>
@@ -7501,15 +7501,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="3" t="n">
+        <v>1.357603</v>
       </c>
       <c r="K129" s="3" t="n">
         <v>1.673832</v>
@@ -7831,15 +7827,11 @@
       <c r="H135" s="3" t="n">
         <v>-0.046173</v>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I135" s="3" t="n">
+        <v>0.010025</v>
+      </c>
+      <c r="J135" s="3" t="n">
+        <v>-0.37842</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.736531</v>
@@ -11951,7 +11943,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>-</t>
@@ -14288,7 +14284,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -15376,7 +15376,11 @@
           <t>Cash flows generated from (used in) operating activities</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -18286,7 +18290,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -22243,7 +22251,11 @@
           <t>Income tax recovery (Note 16 &amp; 18)</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -22791,7 +22803,11 @@
           <t>Income tax recovery (Note 14)</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
